--- a/Shared/XLS/Npc.xlsx
+++ b/Shared/XLS/Npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>!Table</t>
   </si>
@@ -384,6 +384,10 @@
   </si>
   <si>
     <t>Portal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prefab_Npc_Portal</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -1057,7 +1061,7 @@
     <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="20.25" style="1" bestFit="1" customWidth="1"/>
@@ -1224,6 +1228,9 @@
       </c>
       <c r="E7" s="11" t="s">
         <v>64</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -1563,7 +1570,12 @@
       <c r="B4" s="1">
         <v>1</v>
       </c>
-      <c r="D4"/>
+      <c r="C4" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11" t="b">
         <v>0</v>
@@ -1583,7 +1595,12 @@
       <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="D5"/>
+      <c r="C5" s="1">
+        <v>1002</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11" t="b">
         <v>1</v>
@@ -1600,7 +1617,15 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
-      <c r="D6"/>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="J6" s="11"/>
@@ -1614,7 +1639,18 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
-      <c r="D7"/>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4</v>
+      </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="J7" s="11"/>

--- a/Shared/XLS/Npc.xlsx
+++ b/Shared/XLS/Npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="12675" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="8" r:id="rId1"/>
@@ -89,10 +89,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>NpcType</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>FunctionID</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -388,6 +384,10 @@
   </si>
   <si>
     <t>Prefab_Npc_Portal</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>NpcType</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -597,7 +597,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -652,6 +652,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -935,7 +938,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -961,40 +964,40 @@
         <v>5</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1007,40 +1010,40 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>40</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1079,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -1093,17 +1096,17 @@
       <c r="D2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="16" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
@@ -1125,10 +1128,10 @@
         <v>7</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" s="16" t="s">
         <v>7</v>
@@ -1150,13 +1153,13 @@
         <v>1001</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
@@ -1174,13 +1177,13 @@
         <v>1002</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F5" s="11"/>
       <c r="H5" s="11"/>
@@ -1198,13 +1201,13 @@
         <v>1003</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -1221,16 +1224,16 @@
         <v>1004</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="H7" s="11"/>
       <c r="I7" s="11"/>
@@ -1495,7 +1498,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" s="18"/>
     </row>
@@ -1505,22 +1508,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="G2" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>29</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>30</v>
       </c>
       <c r="I2" s="16"/>
       <c r="J2" s="16"/>
@@ -1538,22 +1541,22 @@
         <v>3</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
@@ -1890,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="18"/>
     </row>
@@ -1900,16 +1903,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>33</v>
-      </c>
       <c r="F2" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
@@ -1925,16 +1928,16 @@
         <v>3</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
@@ -1954,10 +1957,10 @@
       </c>
       <c r="D4"/>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -1978,10 +1981,10 @@
         <v>2000010</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -2003,10 +2006,10 @@
         <v>2000010</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -2028,10 +2031,10 @@
         <v>2000010</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
